--- a/r5-TC-FHIR-AG-Scheduling-R5-105-16---grafik-ergänzen/StructureDefinition-at-scheduling-appointment.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-105-16---grafik-ergänzen/StructureDefinition-at-scheduling-appointment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T11:03:45+00:00</t>
+    <t>2026-03-06T11:19:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-105-16---grafik-ergänzen/StructureDefinition-at-scheduling-appointment.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-105-16---grafik-ergänzen/StructureDefinition-at-scheduling-appointment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T11:19:51+00:00</t>
+    <t>2026-03-11T07:45:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-105-16---grafik-ergänzen/StructureDefinition-at-scheduling-appointment.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-105-16---grafik-ergänzen/StructureDefinition-at-scheduling-appointment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T09:25:26+00:00</t>
+    <t>2026-04-07T09:46:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-105-16---grafik-ergänzen/StructureDefinition-at-scheduling-appointment.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-105-16---grafik-ergänzen/StructureDefinition-at-scheduling-appointment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T09:46:48+00:00</t>
+    <t>2026-06-09T10:31:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-105-16---grafik-ergänzen/StructureDefinition-at-scheduling-appointment.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-105-16---grafik-ergänzen/StructureDefinition-at-scheduling-appointment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T10:31:34+00:00</t>
+    <t>2026-06-09T10:57:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-105-16---grafik-ergänzen/StructureDefinition-at-scheduling-appointment.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-105-16---grafik-ergänzen/StructureDefinition-at-scheduling-appointment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T10:57:01+00:00</t>
+    <t>2026-06-09T12:42:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
